--- a/bom/TaloNet_BOM.xlsx
+++ b/bom/TaloNet_BOM.xlsx
@@ -17,7 +17,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shop Tools &amp; Equipment" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost Roll-up" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Drone — Airframe &amp; Propulsion'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Drone — Avionics, Power &amp; C2'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Drone — Net Payload'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Forensic Appliance (ForensIQ-1)'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Fasteners, Wiring &amp; Consumables'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Outsourced Fabrication'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Shop Tools &amp; Equipment'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -570,7 +578,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -589,7 +597,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>그물매 net-interceptor drone + ForensIQ-1 forensic appliance</t>
+          <t>Peregrine net-interceptor drone + ForensIQ-1 forensic appliance</t>
         </is>
       </c>
     </row>
@@ -682,7 +690,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -690,7 +700,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -789,7 +799,7 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-DECK (CNC)</t>
+          <t>TaloNet PG-DECK (CNC)</t>
         </is>
       </c>
       <c r="E2" s="14" t="n">
@@ -903,7 +913,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-MNT (CNC)</t>
+          <t>TaloNet PG-MNT (CNC)</t>
         </is>
       </c>
       <c r="E4" s="14" t="n">
@@ -1017,7 +1027,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-GEAR</t>
+          <t>TaloNet PG-GEAR</t>
         </is>
       </c>
       <c r="E6" s="14" t="n">
@@ -1239,7 +1249,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1247,7 +1259,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1967,7 +1979,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1975,7 +1989,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2188,7 +2202,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-GIMBAL</t>
+          <t>TaloNet PG-GIMBAL</t>
         </is>
       </c>
       <c r="E4" s="14" t="n">
@@ -2473,7 +2487,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-SPOOL</t>
+          <t>TaloNet PG-SPOOL</t>
         </is>
       </c>
       <c r="E9" s="14" t="n">
@@ -3043,7 +3057,7 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-MUZZLE</t>
+          <t>TaloNet PG-MUZZLE</t>
         </is>
       </c>
       <c r="E19" s="14" t="n">
@@ -3100,7 +3114,7 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-PAYIF rev A</t>
+          <t>TaloNet PG-PAYIF rev A</t>
         </is>
       </c>
       <c r="E20" s="14" t="n">
@@ -3151,7 +3165,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3159,7 +3175,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4107,7 +4123,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4115,7 +4133,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4607,7 +4625,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4615,7 +4635,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4771,7 +4791,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>TaloNet GM-PAYIF rev A</t>
+          <t>TaloNet PG-PAYIF rev A</t>
         </is>
       </c>
       <c r="E3" s="14" t="n">
@@ -4879,7 +4899,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4887,7 +4909,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5379,7 +5401,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5387,7 +5411,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -5519,6 +5543,8 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/bom/TaloNet_BOM.xlsx
+++ b/bom/TaloNet_BOM.xlsx
@@ -1991,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3154,13 +3154,412 @@
       </c>
     </row>
     <row r="21">
-      <c r="H21" s="18" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-020</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Trawler</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Large-bore stand-off net launcher (CO2 solenoid + 33 g cartridge)</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>12V NC CO2 solenoid HP</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>55</v>
+      </c>
+      <c r="I21" s="16">
+        <f>E21*H21</f>
+        <v/>
+      </c>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>Industrial supply</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>docs/06</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>RELAY1 fired; large net vs kamikaze</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-021</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Trawler</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>TRAWLER fire MOSFET + arming relay + flyback</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>IRLB3034 + Omron G5LE</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I22" s="16">
+        <f>E22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Mouser</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>docs/06</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>RELAY1 drive + interlock</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-022</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Cord-cut</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Cord-cutter: nichrome burn-wire element + ceramic holder</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>Nichrome 24AWG + holder</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>MAKE</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="16">
+        <f>E23*H23</f>
+        <v/>
+      </c>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>cad</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>RELAY2 tether sever (consumable element)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-023</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Cord-cut</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Cord-cutter driver: power MOSFET + arming relay + flyback</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>IRLB3034 + G5LE + 1N5408</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" s="16">
+        <f>E24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Mouser</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>docs/06</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>RELAY2 burn-wire drive + interlock</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-024</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>TRAWLER large net, knotless Dyneema/Kevlar, ~6.5 m mouth, HD mesh</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Custom cast net (large)</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>ea</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>MAKE</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="I25" s="16">
+        <f>E25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="12" t="inlineStr">
+        <is>
+          <t>Garage / net maker</t>
+        </is>
+      </c>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>cad</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>trawler_net(); stand-off casting net</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-025</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>TRAWLER rim weights (heavy) + heavy tether (Dyneema 3 mm)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Brass weights + Dyneema</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>MAKE</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="I26" s="16">
+        <f>E26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>cad</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>wider spread + severable tether</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>DR-NP-026</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>TRAWLER muzzle / canister housing (printed)</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>TaloNet PG-TRAWL-MUZZLE</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>set</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>MAKE</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="I27" s="16">
+        <f>E27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>Garage 3D print</t>
+        </is>
+      </c>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>cad</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>trawler_launcher()</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="I21" s="19">
-        <f>SUM(I2:I20)</f>
+      <c r="I28" s="19">
+        <f>SUM(I2:I27)</f>
         <v/>
       </c>
     </row>
@@ -5461,7 +5860,7 @@
         </is>
       </c>
       <c r="B4" s="24">
-        <f>'Drone — Net Payload'!I21</f>
+        <f>'Drone — Net Payload'!I28</f>
         <v/>
       </c>
     </row>
